--- a/95_Excel/Excel_Introduction.xlsx
+++ b/95_Excel/Excel_Introduction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ulsc\OneDrive - AspIT - Ondrive\Uli\Python\AspIT_Python\95_Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B79D290-3A48-4CC6-95D7-6B2855D6A8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA9AAD0D-C14D-4B70-8EDA-294024B5A090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1542,6 +1542,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6228BEAA-1775-4BCB-8D39-2614B129552E}">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A1:M20"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1678,6 +1681,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FA42889-8202-43A2-9CA9-4E29B982C8DC}">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1859,6 +1865,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <tabColor theme="9" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultColWidth="36.5546875" defaultRowHeight="19.2" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
